--- a/docs/workbook-split/dateien/D Liquidität.xlsx
+++ b/docs/workbook-split/dateien/D Liquidität.xlsx
@@ -30069,6 +30069,8 @@
         </is>
       </c>
     </row>
+    <row r="686"/>
+    <row r="687"/>
     <row r="688">
       <c r="C688" t="inlineStr">
         <is>
